--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="241">
   <si>
     <t>ID</t>
   </si>
@@ -717,6 +717,12 @@
   </si>
   <si>
     <t>Sentenza di riconoscimento giudiziale della cittadinanza italiana</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Copia dell'atto di cittadinanza che contiene l'esito di accertamento rilasciato dal consolato</t>
   </si>
   <si>
     <t>998</t>
@@ -787,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
@@ -2726,7 +2732,7 @@
         <v>236</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>8</v>
@@ -2750,6 +2756,23 @@
       </c>
       <c r="E115" s="2" t="s">
         <v>237</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="251">
   <si>
     <t>ID</t>
   </si>
@@ -116,7 +116,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Copia dell'atto di assenso del figlio</t>
+    <t>Copia dell'atto di dichiarazione/assenso del figlio</t>
   </si>
   <si>
     <t>15</t>
@@ -729,6 +729,30 @@
   </si>
   <si>
     <t>Atto di costituzione e traduzione</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>Copia sentenza/decreto</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>Atto di pre-riconoscimento dell'altro genitore</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>Provvedimento di riconoscimento della sentenza straniera</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Certificato di cittadinanza straniera o Riconoscimento dello status di apolide del minore</t>
   </si>
   <si>
     <t>998</t>
@@ -799,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
@@ -2772,7 +2796,7 @@
         <v>240</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>8</v>
@@ -2789,13 +2813,81 @@
         <v>242</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>241</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
